--- a/assets/constructions/examples/ctd_ne2_countercone.xlsx
+++ b/assets/constructions/examples/ctd_ne2_countercone.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,727 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>hand</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C3139080</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C3139</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>YG1/25 RUS_Сверление 2025</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>±0.05</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>HA-6</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>1131.05</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C3109100</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C3109</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>YG1/25 RUS_Сверление 2025</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>+0.3;0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>HA-6</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>1009.77</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C3119350</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C3119</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>YG1/25 RUS_Сверление 2025</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>+0.3;0</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>HA-16</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
+        <v>7267.89</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>PMKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C1139115</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C1139</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>HSSCo8</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>56</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>YG1/25 RUS_Сверление 2025</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>±0.05</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>HA-8</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>1896.51</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PMKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C1139250</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C1139</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>h9</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>HSSCo8</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>YG1/25 RUS_Сверление 2025</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>±0.05</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>HA-10</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
+        <v>4539.14</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
